--- a/test/006_UT-名寄せバッチ処理テスト/名寄せテスト証跡.xlsx
+++ b/test/006_UT-名寄せバッチ処理テスト/名寄せテスト証跡.xlsx
@@ -264,6 +264,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="5200650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="5200650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="5200650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -59168,12 +59258,8 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="200" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>※ スクリーンショットをここに貼付</t>
-        </is>
-      </c>
+    <row r="8" ht="409.5" customHeight="1">
+      <c r="A8" s="14" t="n"/>
     </row>
     <row r="9"/>
     <row r="10"/>
@@ -59199,6 +59285,7 @@
     <mergeCell ref="B3:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -59270,12 +59357,8 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="200" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>※ スクリーンショットをここに貼付</t>
-        </is>
-      </c>
+    <row r="8" ht="409.5" customHeight="1">
+      <c r="A8" s="14" t="n"/>
     </row>
     <row r="9"/>
     <row r="10"/>
@@ -59301,6 +59384,7 @@
     <mergeCell ref="B3:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -59372,12 +59456,8 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="200" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>※ スクリーンショットをここに貼付</t>
-        </is>
-      </c>
+    <row r="8" ht="409.5" customHeight="1">
+      <c r="A8" s="14" t="n"/>
     </row>
     <row r="9"/>
     <row r="10"/>
@@ -59403,5 +59483,6 @@
     <mergeCell ref="B3:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>